--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555523496</v>
+        <v>46157.93112809928</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112809928</v>
+        <v>46157.93136867105</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93136867105</v>
+        <v>46157.93384203668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384203668</v>
+        <v>46157.93696004809</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696004809</v>
+        <v>46158.28205058669</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205058669</v>
+        <v>46158.29652613941</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29652613941</v>
+        <v>46158.29807657412</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807657412</v>
+        <v>46158.3337063363</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3337063363</v>
+        <v>46158.37221869495</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Апрель 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221869495</v>
+        <v>46158.3727572844</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
